--- a/results/pooling_analysis/plots/table_pooling_scores.xlsx
+++ b/results/pooling_analysis/plots/table_pooling_scores.xlsx
@@ -482,13 +482,13 @@
         <v>0.01732332461181992</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03808620424317247</v>
+        <v>-0.03808620424317247</v>
       </c>
       <c r="G2" t="n">
         <v>0.0296293500169875</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.06581013639830857</v>
+        <v>0.06581013639830857</v>
       </c>
       <c r="I2" t="n">
         <v>0.09382844717944377</v>
@@ -513,13 +513,13 @@
         <v>0.01050620168166679</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03777162494409526</v>
+        <v>-0.03777162494409526</v>
       </c>
       <c r="G3" t="n">
         <v>0.01911506736342853</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05165759084589615</v>
+        <v>-0.05165759084589615</v>
       </c>
       <c r="I3" t="n">
         <v>0.05472815066104132</v>
@@ -544,13 +544,13 @@
         <v>0.01561936935619192</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1670992889069919</v>
+        <v>0.1670992889069919</v>
       </c>
       <c r="G4" t="n">
         <v>0.04992636164231155</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2276477907001253</v>
+        <v>0.2276477907001253</v>
       </c>
       <c r="I4" t="n">
         <v>0.08128982634049721</v>
@@ -575,13 +575,13 @@
         <v>0.0150683185969201</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1946808391989596</v>
+        <v>0.1946808391989596</v>
       </c>
       <c r="G5" t="n">
         <v>0.03572059984063174</v>
       </c>
       <c r="H5" t="n">
-        <v>0.005164915639608788</v>
+        <v>-0.005164915639608788</v>
       </c>
       <c r="I5" t="n">
         <v>0.04755855260417297</v>
@@ -606,13 +606,13 @@
         <v>0.01012992143103843</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1761783760893939</v>
+        <v>0.1761783760893939</v>
       </c>
       <c r="G6" t="n">
         <v>0.0213457482324639</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07041101694960018</v>
+        <v>-0.07041101694960018</v>
       </c>
       <c r="I6" t="n">
         <v>0.0234817677871987</v>
@@ -637,13 +637,13 @@
         <v>0.009042843816362351</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1639887417351132</v>
+        <v>0.1639887417351132</v>
       </c>
       <c r="G7" t="n">
         <v>0.01544232504693663</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08675546293476862</v>
+        <v>-0.08675546293476862</v>
       </c>
       <c r="I7" t="n">
         <v>0.02219446151151826</v>
@@ -668,13 +668,13 @@
         <v>0.006526638722782579</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1542921317026854</v>
+        <v>0.1542921317026854</v>
       </c>
       <c r="G8" t="n">
         <v>0.01465453887158788</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09166347728937631</v>
+        <v>-0.09166347728937631</v>
       </c>
       <c r="I8" t="n">
         <v>0.01611899033255471</v>
@@ -699,13 +699,13 @@
         <v>0.00336205055667273</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1170062488002875</v>
+        <v>0.1170062488002875</v>
       </c>
       <c r="G9" t="n">
         <v>0.009213156515531723</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09394503570713438</v>
+        <v>-0.09394503570713438</v>
       </c>
       <c r="I9" t="n">
         <v>0.01228228669918006</v>
@@ -730,13 +730,13 @@
         <v>0.001451469885936801</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.07705970492335926</v>
+        <v>0.07705970492335926</v>
       </c>
       <c r="G10" t="n">
         <v>0.004725341228493098</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1123821329437714</v>
+        <v>-0.1123821329437714</v>
       </c>
       <c r="I10" t="n">
         <v>0.008794128060667719</v>
